--- a/input/validation/10-5/instance-5.xlsx
+++ b/input/validation/10-5/instance-5.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N49"/>
+  <dimension ref="A1:N51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -514,7 +514,7 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>49</v>
+        <v>22</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -531,22 +531,22 @@
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>9.333333333333334</v>
+        <v>1</v>
       </c>
       <c r="J2" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="N2" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -562,7 +562,7 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>49</v>
+        <v>22</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -576,25 +576,25 @@
         <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>9.333333333333334</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="J3" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="K3" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="L3" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -610,7 +610,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>49</v>
+        <v>22</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -624,16 +624,16 @@
         <v>2</v>
       </c>
       <c r="H4" t="n">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="I4" t="n">
-        <v>33</v>
+        <v>15.5</v>
       </c>
       <c r="J4" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -642,7 +642,7 @@
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5">
@@ -658,7 +658,7 @@
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>49</v>
+        <v>22</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -672,25 +672,25 @@
         <v>3</v>
       </c>
       <c r="H5" t="n">
-        <v>33</v>
+        <v>15.5</v>
       </c>
       <c r="I5" t="n">
-        <v>40</v>
+        <v>18.5</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M5" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -703,10 +703,10 @@
         <v>1</v>
       </c>
       <c r="C6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D6" t="n">
-        <v>43</v>
+        <v>74</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -720,25 +720,25 @@
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I6" t="n">
+        <v>12.25</v>
+      </c>
+      <c r="J6" t="n">
+        <v>6</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>6</v>
+      </c>
+      <c r="M6" t="n">
+        <v>6</v>
+      </c>
+      <c r="N6" t="n">
         <v>7</v>
-      </c>
-      <c r="J6" t="n">
-        <v>3</v>
-      </c>
-      <c r="K6" t="n">
-        <v>3</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>3</v>
-      </c>
-      <c r="N6" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -751,10 +751,10 @@
         <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>43</v>
+        <v>74</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>1</v>
       </c>
       <c r="H7" t="n">
+        <v>12.25</v>
+      </c>
+      <c r="I7" t="n">
+        <v>18.58333333333333</v>
+      </c>
+      <c r="J7" t="n">
         <v>7</v>
       </c>
-      <c r="I7" t="n">
-        <v>17</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -786,7 +786,7 @@
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8">
@@ -799,10 +799,10 @@
         <v>1</v>
       </c>
       <c r="C8" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D8" t="n">
-        <v>43</v>
+        <v>74</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -816,22 +816,22 @@
         <v>2</v>
       </c>
       <c r="H8" t="n">
-        <v>17</v>
+        <v>18.58333333333333</v>
       </c>
       <c r="I8" t="n">
-        <v>22</v>
+        <v>24.58333333333333</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
@@ -847,10 +847,10 @@
         <v>1</v>
       </c>
       <c r="C9" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D9" t="n">
-        <v>43</v>
+        <v>74</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -864,25 +864,25 @@
         <v>3</v>
       </c>
       <c r="H9" t="n">
-        <v>22</v>
+        <v>24.58333333333333</v>
       </c>
       <c r="I9" t="n">
-        <v>28</v>
+        <v>32.91666666666666</v>
       </c>
       <c r="J9" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="N9" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10">
@@ -895,10 +895,10 @@
         <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D10" t="n">
-        <v>43</v>
+        <v>74</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -912,73 +912,73 @@
         <v>4</v>
       </c>
       <c r="H10" t="n">
-        <v>28</v>
+        <v>32.91666666666666</v>
       </c>
       <c r="I10" t="n">
-        <v>39</v>
+        <v>43.11666666666666</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="N10" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J-2</t>
+          <t>J-1</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="D11" t="n">
-        <v>48</v>
+        <v>74</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>O-20</t>
+          <t>O-15</t>
         </is>
       </c>
       <c r="F11" t="n">
         <v>9</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H11" t="n">
-        <v>14</v>
+        <v>43.11666666666666</v>
       </c>
       <c r="I11" t="n">
+        <v>60.78333333333333</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>20</v>
+      </c>
+      <c r="L11" t="n">
+        <v>15</v>
+      </c>
+      <c r="M11" t="n">
         <v>18</v>
       </c>
-      <c r="J11" t="n">
-        <v>4</v>
-      </c>
-      <c r="K11" t="n">
-        <v>4</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>4</v>
-      </c>
       <c r="N11" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -991,42 +991,42 @@
         <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D12" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>O-21</t>
+          <t>O-20</t>
         </is>
       </c>
       <c r="F12" t="n">
         <v>10</v>
       </c>
       <c r="G12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
+        <v>16</v>
+      </c>
+      <c r="I12" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="J12" t="n">
         <v>18</v>
       </c>
-      <c r="I12" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="J12" t="n">
-        <v>5</v>
-      </c>
       <c r="K12" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="L12" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="M12" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="N12" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13">
@@ -1039,42 +1039,42 @@
         <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D13" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>O-22</t>
+          <t>O-21</t>
         </is>
       </c>
       <c r="F13" t="n">
         <v>11</v>
       </c>
       <c r="G13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>23.2</v>
+        <v>31.4</v>
       </c>
       <c r="I13" t="n">
-        <v>32.2</v>
+        <v>44.06666666666666</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="14">
@@ -1087,90 +1087,90 @@
         <v>2</v>
       </c>
       <c r="C14" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D14" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>O-23</t>
+          <t>O-22</t>
         </is>
       </c>
       <c r="F14" t="n">
         <v>12</v>
       </c>
       <c r="G14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H14" t="n">
-        <v>32.2</v>
+        <v>44.06666666666666</v>
       </c>
       <c r="I14" t="n">
-        <v>53.2</v>
+        <v>54.46666666666666</v>
       </c>
       <c r="J14" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="L14" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>J-3</t>
+          <t>J-2</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D15" t="n">
-        <v>78</v>
+        <v>54</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>O-30</t>
+          <t>O-23</t>
         </is>
       </c>
       <c r="F15" t="n">
         <v>13</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H15" t="n">
-        <v>19</v>
+        <v>54.46666666666666</v>
       </c>
       <c r="I15" t="n">
-        <v>33</v>
+        <v>55.46666666666666</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L15" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1183,42 +1183,42 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D16" t="n">
-        <v>78</v>
+        <v>97</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>O-31</t>
+          <t>O-30</t>
         </is>
       </c>
       <c r="F16" t="n">
         <v>14</v>
       </c>
       <c r="G16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="I16" t="n">
-        <v>54</v>
+        <v>32.2</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="L16" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
     <row r="17">
@@ -1231,42 +1231,42 @@
         <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>97</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>O-32</t>
+          <t>O-31</t>
         </is>
       </c>
       <c r="F17" t="n">
         <v>15</v>
       </c>
       <c r="G17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H17" t="n">
-        <v>54</v>
+        <v>32.2</v>
       </c>
       <c r="I17" t="n">
-        <v>61.2</v>
+        <v>50.53333333333333</v>
       </c>
       <c r="J17" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="L17" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="M17" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="N17" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1279,33 +1279,33 @@
         <v>3</v>
       </c>
       <c r="C18" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D18" t="n">
-        <v>78</v>
+        <v>97</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>O-33</t>
+          <t>O-32</t>
         </is>
       </c>
       <c r="F18" t="n">
         <v>16</v>
       </c>
       <c r="G18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H18" t="n">
-        <v>61.2</v>
+        <v>50.53333333333333</v>
       </c>
       <c r="I18" t="n">
-        <v>68.7</v>
+        <v>63.53333333333333</v>
       </c>
       <c r="J18" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="K18" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -1314,7 +1314,7 @@
         <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
     </row>
     <row r="19">
@@ -1327,42 +1327,42 @@
         <v>3</v>
       </c>
       <c r="C19" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D19" t="n">
-        <v>78</v>
+        <v>97</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>O-34</t>
+          <t>O-33</t>
         </is>
       </c>
       <c r="F19" t="n">
         <v>17</v>
       </c>
       <c r="G19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H19" t="n">
-        <v>68.7</v>
+        <v>63.53333333333333</v>
       </c>
       <c r="I19" t="n">
-        <v>70.7</v>
+        <v>74.03333333333333</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="K19" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="L19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20">
@@ -1375,90 +1375,90 @@
         <v>3</v>
       </c>
       <c r="C20" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D20" t="n">
-        <v>78</v>
+        <v>97</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>O-35</t>
+          <t>O-34</t>
         </is>
       </c>
       <c r="F20" t="n">
         <v>18</v>
       </c>
       <c r="G20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H20" t="n">
-        <v>70.7</v>
+        <v>74.03333333333333</v>
       </c>
       <c r="I20" t="n">
-        <v>82.03333333333333</v>
+        <v>84.03333333333333</v>
       </c>
       <c r="J20" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J-4</t>
+          <t>J-3</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C21" t="n">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="D21" t="n">
-        <v>76</v>
+        <v>97</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>O-40</t>
+          <t>O-35</t>
         </is>
       </c>
       <c r="F21" t="n">
         <v>19</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H21" t="n">
-        <v>29</v>
+        <v>84.03333333333333</v>
       </c>
       <c r="I21" t="n">
-        <v>39.75</v>
+        <v>95.36666666666666</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="K21" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="L21" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
         <v>12</v>
-      </c>
-      <c r="N21" t="n">
-        <v>9</v>
       </c>
     </row>
     <row r="22">
@@ -1471,42 +1471,42 @@
         <v>4</v>
       </c>
       <c r="C22" t="n">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="D22" t="n">
-        <v>76</v>
+        <v>62</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>O-41</t>
+          <t>O-40</t>
         </is>
       </c>
       <c r="F22" t="n">
         <v>20</v>
       </c>
       <c r="G22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>39.75</v>
+        <v>19</v>
       </c>
       <c r="I22" t="n">
-        <v>56.75</v>
+        <v>20</v>
       </c>
       <c r="J22" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="K22" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1519,42 +1519,42 @@
         <v>4</v>
       </c>
       <c r="C23" t="n">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="D23" t="n">
-        <v>76</v>
+        <v>62</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>O-42</t>
+          <t>O-41</t>
         </is>
       </c>
       <c r="F23" t="n">
         <v>21</v>
       </c>
       <c r="G23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H23" t="n">
-        <v>56.75</v>
+        <v>20</v>
       </c>
       <c r="I23" t="n">
-        <v>62.75</v>
+        <v>36.75</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="L23" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
     <row r="24">
@@ -1567,42 +1567,42 @@
         <v>4</v>
       </c>
       <c r="C24" t="n">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="D24" t="n">
-        <v>76</v>
+        <v>62</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>O-43</t>
+          <t>O-42</t>
         </is>
       </c>
       <c r="F24" t="n">
         <v>22</v>
       </c>
       <c r="G24" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H24" t="n">
-        <v>62.75</v>
+        <v>36.75</v>
       </c>
       <c r="I24" t="n">
-        <v>82.34999999999999</v>
+        <v>43.41666666666666</v>
       </c>
       <c r="J24" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="L24" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="N24" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
     </row>
     <row r="25">
@@ -1615,90 +1615,90 @@
         <v>4</v>
       </c>
       <c r="C25" t="n">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="D25" t="n">
-        <v>76</v>
+        <v>62</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>O-44</t>
+          <t>O-43</t>
         </is>
       </c>
       <c r="F25" t="n">
         <v>23</v>
       </c>
       <c r="G25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H25" t="n">
-        <v>82.34999999999999</v>
+        <v>43.41666666666666</v>
       </c>
       <c r="I25" t="n">
-        <v>88.14999999999999</v>
+        <v>45.41666666666666</v>
       </c>
       <c r="J25" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="K25" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M25" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N25" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>J-5</t>
+          <t>J-4</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C26" t="n">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="D26" t="n">
-        <v>46</v>
+        <v>62</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>O-50</t>
+          <t>O-44</t>
         </is>
       </c>
       <c r="F26" t="n">
         <v>24</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H26" t="n">
-        <v>31</v>
+        <v>45.41666666666666</v>
       </c>
       <c r="I26" t="n">
-        <v>32</v>
+        <v>64.81666666666666</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="L26" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="M26" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="N26" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
     </row>
     <row r="27">
@@ -1711,42 +1711,42 @@
         <v>5</v>
       </c>
       <c r="C27" t="n">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="D27" t="n">
-        <v>46</v>
+        <v>85</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>O-51</t>
+          <t>O-50</t>
         </is>
       </c>
       <c r="F27" t="n">
         <v>25</v>
       </c>
       <c r="G27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="I27" t="n">
-        <v>49.8</v>
+        <v>31</v>
       </c>
       <c r="J27" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="K27" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="L27" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="M27" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="N27" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
     </row>
     <row r="28">
@@ -1759,39 +1759,39 @@
         <v>5</v>
       </c>
       <c r="C28" t="n">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="D28" t="n">
-        <v>46</v>
+        <v>85</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>O-52</t>
+          <t>O-51</t>
         </is>
       </c>
       <c r="F28" t="n">
         <v>26</v>
       </c>
       <c r="G28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H28" t="n">
-        <v>49.8</v>
+        <v>31</v>
       </c>
       <c r="I28" t="n">
-        <v>56.8</v>
+        <v>50.33333333333333</v>
       </c>
       <c r="J28" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="K28" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="M28" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="N28" t="n">
         <v>0</v>
@@ -1807,39 +1807,39 @@
         <v>5</v>
       </c>
       <c r="C29" t="n">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="D29" t="n">
-        <v>46</v>
+        <v>85</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>O-53</t>
+          <t>O-52</t>
         </is>
       </c>
       <c r="F29" t="n">
         <v>27</v>
       </c>
       <c r="G29" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H29" t="n">
-        <v>56.8</v>
+        <v>50.33333333333333</v>
       </c>
       <c r="I29" t="n">
-        <v>66.05</v>
+        <v>61.83333333333333</v>
       </c>
       <c r="J29" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="K29" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="N29" t="n">
         <v>0</v>
@@ -1848,46 +1848,46 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>J-6</t>
+          <t>J-5</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C30" t="n">
-        <v>45</v>
+        <v>22</v>
       </c>
       <c r="D30" t="n">
-        <v>46</v>
+        <v>85</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>O-60</t>
+          <t>O-53</t>
         </is>
       </c>
       <c r="F30" t="n">
         <v>28</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H30" t="n">
-        <v>45</v>
+        <v>61.83333333333333</v>
       </c>
       <c r="I30" t="n">
-        <v>48</v>
+        <v>80.33333333333333</v>
       </c>
       <c r="J30" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M30" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
         <v>0</v>
@@ -1896,49 +1896,49 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>J-6</t>
+          <t>J-5</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C31" t="n">
-        <v>45</v>
+        <v>22</v>
       </c>
       <c r="D31" t="n">
-        <v>46</v>
+        <v>85</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>O-61</t>
+          <t>O-54</t>
         </is>
       </c>
       <c r="F31" t="n">
         <v>29</v>
       </c>
       <c r="G31" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H31" t="n">
-        <v>48</v>
+        <v>80.33333333333333</v>
       </c>
       <c r="I31" t="n">
-        <v>60.6</v>
+        <v>87.33333333333333</v>
       </c>
       <c r="J31" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="K31" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="L31" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -1951,42 +1951,42 @@
         <v>6</v>
       </c>
       <c r="C32" t="n">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="D32" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>O-62</t>
+          <t>O-60</t>
         </is>
       </c>
       <c r="F32" t="n">
         <v>30</v>
       </c>
       <c r="G32" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>60.6</v>
+        <v>26</v>
       </c>
       <c r="I32" t="n">
-        <v>66.26666666666667</v>
+        <v>39</v>
       </c>
       <c r="J32" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="N32" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -1999,39 +1999,39 @@
         <v>6</v>
       </c>
       <c r="C33" t="n">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="D33" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>O-63</t>
+          <t>O-61</t>
         </is>
       </c>
       <c r="F33" t="n">
         <v>31</v>
       </c>
       <c r="G33" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H33" t="n">
-        <v>66.26666666666667</v>
+        <v>39</v>
       </c>
       <c r="I33" t="n">
-        <v>73.26666666666667</v>
+        <v>59</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
         <v>0</v>
@@ -2047,33 +2047,33 @@
         <v>6</v>
       </c>
       <c r="C34" t="n">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="D34" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>O-64</t>
+          <t>O-62</t>
         </is>
       </c>
       <c r="F34" t="n">
         <v>32</v>
       </c>
       <c r="G34" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H34" t="n">
-        <v>73.26666666666667</v>
+        <v>59</v>
       </c>
       <c r="I34" t="n">
-        <v>82.26666666666667</v>
+        <v>65</v>
       </c>
       <c r="J34" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
@@ -2088,49 +2088,49 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>J-7</t>
+          <t>J-6</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C35" t="n">
-        <v>61</v>
+        <v>26</v>
       </c>
       <c r="D35" t="n">
-        <v>97</v>
+        <v>48</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>O-70</t>
+          <t>O-63</t>
         </is>
       </c>
       <c r="F35" t="n">
         <v>33</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H35" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="I35" t="n">
-        <v>75.25</v>
+        <v>66</v>
       </c>
       <c r="J35" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M35" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -2143,27 +2143,27 @@
         <v>7</v>
       </c>
       <c r="C36" t="n">
-        <v>61</v>
+        <v>32</v>
       </c>
       <c r="D36" t="n">
-        <v>97</v>
+        <v>70</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>O-71</t>
+          <t>O-70</t>
         </is>
       </c>
       <c r="F36" t="n">
         <v>34</v>
       </c>
       <c r="G36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>75.25</v>
+        <v>32</v>
       </c>
       <c r="I36" t="n">
-        <v>90.25</v>
+        <v>36</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2172,13 +2172,13 @@
         <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M36" t="n">
         <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -2191,42 +2191,42 @@
         <v>7</v>
       </c>
       <c r="C37" t="n">
-        <v>61</v>
+        <v>32</v>
       </c>
       <c r="D37" t="n">
-        <v>97</v>
+        <v>70</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>O-72</t>
+          <t>O-71</t>
         </is>
       </c>
       <c r="F37" t="n">
         <v>35</v>
       </c>
       <c r="G37" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H37" t="n">
-        <v>90.25</v>
+        <v>36</v>
       </c>
       <c r="I37" t="n">
-        <v>94.25</v>
+        <v>58.6</v>
       </c>
       <c r="J37" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="K37" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="L37" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="N37" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
     </row>
     <row r="38">
@@ -2239,42 +2239,42 @@
         <v>7</v>
       </c>
       <c r="C38" t="n">
-        <v>61</v>
+        <v>32</v>
       </c>
       <c r="D38" t="n">
-        <v>97</v>
+        <v>70</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>O-73</t>
+          <t>O-72</t>
         </is>
       </c>
       <c r="F38" t="n">
         <v>36</v>
       </c>
       <c r="G38" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H38" t="n">
-        <v>94.25</v>
+        <v>58.6</v>
       </c>
       <c r="I38" t="n">
-        <v>113.25</v>
+        <v>71.93333333333334</v>
       </c>
       <c r="J38" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="M38" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="N38" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
     </row>
     <row r="39">
@@ -2287,42 +2287,42 @@
         <v>7</v>
       </c>
       <c r="C39" t="n">
-        <v>61</v>
+        <v>32</v>
       </c>
       <c r="D39" t="n">
-        <v>97</v>
+        <v>70</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>O-74</t>
+          <t>O-73</t>
         </is>
       </c>
       <c r="F39" t="n">
         <v>37</v>
       </c>
       <c r="G39" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H39" t="n">
-        <v>113.25</v>
+        <v>71.93333333333334</v>
       </c>
       <c r="I39" t="n">
-        <v>114.25</v>
+        <v>74.93333333333334</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M39" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="40">
@@ -2335,42 +2335,42 @@
         <v>7</v>
       </c>
       <c r="C40" t="n">
-        <v>61</v>
+        <v>32</v>
       </c>
       <c r="D40" t="n">
-        <v>97</v>
+        <v>70</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>O-75</t>
+          <t>O-74</t>
         </is>
       </c>
       <c r="F40" t="n">
         <v>38</v>
       </c>
       <c r="G40" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H40" t="n">
-        <v>114.25</v>
+        <v>74.93333333333334</v>
       </c>
       <c r="I40" t="n">
-        <v>133.65</v>
+        <v>87.93333333333334</v>
       </c>
       <c r="J40" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="N40" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -2383,10 +2383,10 @@
         <v>8</v>
       </c>
       <c r="C41" t="n">
-        <v>63</v>
+        <v>36</v>
       </c>
       <c r="D41" t="n">
-        <v>61</v>
+        <v>112</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -2400,19 +2400,19 @@
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>63</v>
+        <v>36</v>
       </c>
       <c r="I41" t="n">
-        <v>76</v>
+        <v>52.66666666666667</v>
       </c>
       <c r="J41" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="K41" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="M41" t="n">
         <v>0</v>
@@ -2431,10 +2431,10 @@
         <v>8</v>
       </c>
       <c r="C42" t="n">
-        <v>63</v>
+        <v>36</v>
       </c>
       <c r="D42" t="n">
-        <v>61</v>
+        <v>112</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -2448,22 +2448,22 @@
         <v>1</v>
       </c>
       <c r="H42" t="n">
-        <v>76</v>
+        <v>52.66666666666667</v>
       </c>
       <c r="I42" t="n">
-        <v>80</v>
+        <v>70.41666666666667</v>
       </c>
       <c r="J42" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="K42" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="N42" t="n">
         <v>0</v>
@@ -2479,10 +2479,10 @@
         <v>8</v>
       </c>
       <c r="C43" t="n">
-        <v>63</v>
+        <v>36</v>
       </c>
       <c r="D43" t="n">
-        <v>61</v>
+        <v>112</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -2496,25 +2496,25 @@
         <v>2</v>
       </c>
       <c r="H43" t="n">
-        <v>80</v>
+        <v>70.41666666666667</v>
       </c>
       <c r="I43" t="n">
-        <v>91</v>
+        <v>85.41666666666667</v>
       </c>
       <c r="J43" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="L43" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
         <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -2527,10 +2527,10 @@
         <v>8</v>
       </c>
       <c r="C44" t="n">
-        <v>63</v>
+        <v>36</v>
       </c>
       <c r="D44" t="n">
-        <v>61</v>
+        <v>112</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -2544,121 +2544,121 @@
         <v>3</v>
       </c>
       <c r="H44" t="n">
-        <v>91</v>
+        <v>85.41666666666667</v>
       </c>
       <c r="I44" t="n">
-        <v>110.6666666666667</v>
+        <v>99.91666666666667</v>
       </c>
       <c r="J44" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="L44" t="n">
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>J-9</t>
+          <t>J-8</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C45" t="n">
-        <v>66</v>
+        <v>36</v>
       </c>
       <c r="D45" t="n">
-        <v>13</v>
+        <v>112</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>O-90</t>
+          <t>O-84</t>
         </is>
       </c>
       <c r="F45" t="n">
         <v>43</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H45" t="n">
-        <v>66</v>
+        <v>99.91666666666667</v>
       </c>
       <c r="I45" t="n">
-        <v>70</v>
+        <v>101.9166666666667</v>
       </c>
       <c r="J45" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K45" t="n">
         <v>0</v>
       </c>
       <c r="L45" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>J-9</t>
+          <t>J-8</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C46" t="n">
-        <v>66</v>
+        <v>36</v>
       </c>
       <c r="D46" t="n">
-        <v>13</v>
+        <v>112</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>O-91</t>
+          <t>O-85</t>
         </is>
       </c>
       <c r="F46" t="n">
         <v>44</v>
       </c>
       <c r="G46" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H46" t="n">
-        <v>70</v>
+        <v>101.9166666666667</v>
       </c>
       <c r="I46" t="n">
-        <v>71</v>
+        <v>124.1166666666667</v>
       </c>
       <c r="J46" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="K46" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="L46" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="M46" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="N46" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
     </row>
     <row r="47">
@@ -2671,42 +2671,42 @@
         <v>9</v>
       </c>
       <c r="C47" t="n">
-        <v>66</v>
+        <v>42</v>
       </c>
       <c r="D47" t="n">
-        <v>13</v>
+        <v>69</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>O-92</t>
+          <t>O-90</t>
         </is>
       </c>
       <c r="F47" t="n">
         <v>45</v>
       </c>
       <c r="G47" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" t="n">
+        <v>42</v>
+      </c>
+      <c r="I47" t="n">
+        <v>44</v>
+      </c>
+      <c r="J47" t="n">
         <v>2</v>
       </c>
-      <c r="H47" t="n">
-        <v>71</v>
-      </c>
-      <c r="I47" t="n">
-        <v>74</v>
-      </c>
-      <c r="J47" t="n">
-        <v>3</v>
-      </c>
       <c r="K47" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L47" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M47" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N47" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="48">
@@ -2719,42 +2719,42 @@
         <v>9</v>
       </c>
       <c r="C48" t="n">
-        <v>66</v>
+        <v>42</v>
       </c>
       <c r="D48" t="n">
-        <v>13</v>
+        <v>69</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>O-93</t>
+          <t>O-91</t>
         </is>
       </c>
       <c r="F48" t="n">
         <v>46</v>
       </c>
       <c r="G48" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H48" t="n">
-        <v>74</v>
+        <v>44</v>
       </c>
       <c r="I48" t="n">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L48" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="M48" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="N48" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
     </row>
     <row r="49">
@@ -2767,42 +2767,138 @@
         <v>9</v>
       </c>
       <c r="C49" t="n">
-        <v>66</v>
+        <v>42</v>
       </c>
       <c r="D49" t="n">
-        <v>13</v>
+        <v>69</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>O-94</t>
+          <t>O-92</t>
         </is>
       </c>
       <c r="F49" t="n">
         <v>47</v>
       </c>
       <c r="G49" t="n">
+        <v>2</v>
+      </c>
+      <c r="H49" t="n">
+        <v>66</v>
+      </c>
+      <c r="I49" t="n">
+        <v>80.40000000000001</v>
+      </c>
+      <c r="J49" t="n">
+        <v>15</v>
+      </c>
+      <c r="K49" t="n">
+        <v>14</v>
+      </c>
+      <c r="L49" t="n">
+        <v>12</v>
+      </c>
+      <c r="M49" t="n">
+        <v>18</v>
+      </c>
+      <c r="N49" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>J-9</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>9</v>
+      </c>
+      <c r="C50" t="n">
+        <v>42</v>
+      </c>
+      <c r="D50" t="n">
+        <v>69</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>O-93</t>
+        </is>
+      </c>
+      <c r="F50" t="n">
+        <v>48</v>
+      </c>
+      <c r="G50" t="n">
+        <v>3</v>
+      </c>
+      <c r="H50" t="n">
+        <v>80.40000000000001</v>
+      </c>
+      <c r="I50" t="n">
+        <v>82.40000000000001</v>
+      </c>
+      <c r="J50" t="n">
+        <v>0</v>
+      </c>
+      <c r="K50" t="n">
+        <v>0</v>
+      </c>
+      <c r="L50" t="n">
+        <v>0</v>
+      </c>
+      <c r="M50" t="n">
+        <v>2</v>
+      </c>
+      <c r="N50" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>J-9</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>9</v>
+      </c>
+      <c r="C51" t="n">
+        <v>42</v>
+      </c>
+      <c r="D51" t="n">
+        <v>69</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>O-94</t>
+        </is>
+      </c>
+      <c r="F51" t="n">
+        <v>49</v>
+      </c>
+      <c r="G51" t="n">
         <v>4</v>
       </c>
-      <c r="H49" t="n">
-        <v>75</v>
-      </c>
-      <c r="I49" t="n">
-        <v>77</v>
-      </c>
-      <c r="J49" t="n">
-        <v>2</v>
-      </c>
-      <c r="K49" t="n">
-        <v>0</v>
-      </c>
-      <c r="L49" t="n">
-        <v>0</v>
-      </c>
-      <c r="M49" t="n">
-        <v>2</v>
-      </c>
-      <c r="N49" t="n">
-        <v>0</v>
+      <c r="H51" t="n">
+        <v>82.40000000000001</v>
+      </c>
+      <c r="I51" t="n">
+        <v>93</v>
+      </c>
+      <c r="J51" t="n">
+        <v>12</v>
+      </c>
+      <c r="K51" t="n">
+        <v>10</v>
+      </c>
+      <c r="L51" t="n">
+        <v>9</v>
+      </c>
+      <c r="M51" t="n">
+        <v>11</v>
+      </c>
+      <c r="N51" t="n">
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -2816,7 +2912,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O5"/>
+  <dimension ref="A1:N1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2890,223 +2986,6 @@
           <t>Machine 4</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>Initial_Machine</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>J-0</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2" t="n">
-        <v>49</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>O-01</t>
-        </is>
-      </c>
-      <c r="F2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H2" t="n">
-        <v>9.333333333333334</v>
-      </c>
-      <c r="I2" t="n">
-        <v>27</v>
-      </c>
-      <c r="J2" t="n">
-        <v>17</v>
-      </c>
-      <c r="K2" t="n">
-        <v>18</v>
-      </c>
-      <c r="L2" t="n">
-        <v>18</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>Machine 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>J-1</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C3" t="n">
-        <v>4</v>
-      </c>
-      <c r="D3" t="n">
-        <v>43</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>O-12</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
-        <v>6</v>
-      </c>
-      <c r="G3" t="n">
-        <v>2</v>
-      </c>
-      <c r="H3" t="n">
-        <v>17</v>
-      </c>
-      <c r="I3" t="n">
-        <v>22</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L3" t="n">
-        <v>5</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>Machine 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>J-2</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>2</v>
-      </c>
-      <c r="C4" t="n">
-        <v>14</v>
-      </c>
-      <c r="D4" t="n">
-        <v>48</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>O-21</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
-        <v>10</v>
-      </c>
-      <c r="G4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H4" t="n">
-        <v>18</v>
-      </c>
-      <c r="I4" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="J4" t="n">
-        <v>5</v>
-      </c>
-      <c r="K4" t="n">
-        <v>6</v>
-      </c>
-      <c r="L4" t="n">
-        <v>6</v>
-      </c>
-      <c r="M4" t="n">
-        <v>4</v>
-      </c>
-      <c r="N4" t="n">
-        <v>5</v>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>Machine 0</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>J-3</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>3</v>
-      </c>
-      <c r="C5" t="n">
-        <v>19</v>
-      </c>
-      <c r="D5" t="n">
-        <v>78</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>O-30</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
-        <v>13</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>19</v>
-      </c>
-      <c r="I5" t="n">
-        <v>33</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>14</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>Buffer</t>
-        </is>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/input/validation/10-5/instance-5.xlsx
+++ b/input/validation/10-5/instance-5.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N51"/>
+  <dimension ref="A1:N52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -514,7 +514,7 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>22</v>
+        <v>74</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -531,22 +531,22 @@
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>1</v>
+        <v>13.25</v>
       </c>
       <c r="J2" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="K2" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="N2" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3">
@@ -562,7 +562,7 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>22</v>
+        <v>74</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -576,25 +576,25 @@
         <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>13.25</v>
       </c>
       <c r="I3" t="n">
-        <v>4</v>
+        <v>34.65</v>
       </c>
       <c r="J3" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="K3" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="N3" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4">
@@ -610,7 +610,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>22</v>
+        <v>74</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -624,25 +624,25 @@
         <v>2</v>
       </c>
       <c r="H4" t="n">
-        <v>4</v>
+        <v>34.65</v>
       </c>
       <c r="I4" t="n">
-        <v>15.5</v>
+        <v>48.31666666666666</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="K4" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="N4" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -658,7 +658,7 @@
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>22</v>
+        <v>74</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -672,25 +672,25 @@
         <v>3</v>
       </c>
       <c r="H5" t="n">
-        <v>15.5</v>
+        <v>48.31666666666666</v>
       </c>
       <c r="I5" t="n">
-        <v>18.5</v>
+        <v>56.11666666666666</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="K5" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="L5" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="N5" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6">
@@ -703,10 +703,10 @@
         <v>1</v>
       </c>
       <c r="C6" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>74</v>
+        <v>46</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -720,25 +720,25 @@
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I6" t="n">
-        <v>12.25</v>
+        <v>15</v>
       </c>
       <c r="J6" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="M6" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -751,10 +751,10 @@
         <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>74</v>
+        <v>46</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -768,25 +768,25 @@
         <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>12.25</v>
+        <v>15</v>
       </c>
       <c r="I7" t="n">
-        <v>18.58333333333333</v>
+        <v>20.4</v>
       </c>
       <c r="J7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K7" t="n">
         <v>5</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N7" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -799,10 +799,10 @@
         <v>1</v>
       </c>
       <c r="C8" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>74</v>
+        <v>46</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -816,25 +816,25 @@
         <v>2</v>
       </c>
       <c r="H8" t="n">
-        <v>18.58333333333333</v>
+        <v>20.4</v>
       </c>
       <c r="I8" t="n">
-        <v>24.58333333333333</v>
+        <v>27.15</v>
       </c>
       <c r="J8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K8" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
         <v>6</v>
       </c>
       <c r="M8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9">
@@ -847,10 +847,10 @@
         <v>1</v>
       </c>
       <c r="C9" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>74</v>
+        <v>46</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -864,118 +864,118 @@
         <v>3</v>
       </c>
       <c r="H9" t="n">
-        <v>24.58333333333333</v>
+        <v>27.15</v>
       </c>
       <c r="I9" t="n">
-        <v>32.91666666666666</v>
+        <v>37.4</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
+        <v>12</v>
+      </c>
+      <c r="L9" t="n">
         <v>8</v>
       </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
       <c r="M9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N9" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J-1</t>
+          <t>J-2</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>74</v>
+        <v>104</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>O-14</t>
+          <t>O-20</t>
         </is>
       </c>
       <c r="F10" t="n">
         <v>8</v>
       </c>
       <c r="G10" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>32.91666666666666</v>
+        <v>5</v>
       </c>
       <c r="I10" t="n">
-        <v>43.11666666666666</v>
+        <v>23.66666666666667</v>
       </c>
       <c r="J10" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="K10" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="N10" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J-1</t>
+          <t>J-2</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>74</v>
+        <v>104</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>O-15</t>
+          <t>O-21</t>
         </is>
       </c>
       <c r="F11" t="n">
         <v>9</v>
       </c>
       <c r="G11" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H11" t="n">
-        <v>43.11666666666666</v>
+        <v>23.66666666666667</v>
       </c>
       <c r="I11" t="n">
-        <v>60.78333333333333</v>
+        <v>39.66666666666667</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="L11" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -991,42 +991,42 @@
         <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>54</v>
+        <v>104</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>O-20</t>
+          <t>O-22</t>
         </is>
       </c>
       <c r="F12" t="n">
         <v>10</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H12" t="n">
-        <v>16</v>
+        <v>39.66666666666667</v>
       </c>
       <c r="I12" t="n">
-        <v>31.4</v>
+        <v>54.66666666666667</v>
       </c>
       <c r="J12" t="n">
         <v>18</v>
       </c>
       <c r="K12" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
+        <v>13</v>
+      </c>
+      <c r="M12" t="n">
         <v>14</v>
       </c>
-      <c r="M12" t="n">
-        <v>16</v>
-      </c>
       <c r="N12" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="13">
@@ -1039,42 +1039,42 @@
         <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>54</v>
+        <v>104</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>O-21</t>
+          <t>O-23</t>
         </is>
       </c>
       <c r="F13" t="n">
         <v>11</v>
       </c>
       <c r="G13" t="n">
+        <v>3</v>
+      </c>
+      <c r="H13" t="n">
+        <v>54.66666666666667</v>
+      </c>
+      <c r="I13" t="n">
+        <v>55.66666666666667</v>
+      </c>
+      <c r="J13" t="n">
         <v>1</v>
       </c>
-      <c r="H13" t="n">
-        <v>31.4</v>
-      </c>
-      <c r="I13" t="n">
-        <v>44.06666666666666</v>
-      </c>
-      <c r="J13" t="n">
-        <v>12</v>
-      </c>
       <c r="K13" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N13" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1087,42 +1087,42 @@
         <v>2</v>
       </c>
       <c r="C14" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="D14" t="n">
-        <v>54</v>
+        <v>104</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>O-22</t>
+          <t>O-24</t>
         </is>
       </c>
       <c r="F14" t="n">
         <v>12</v>
       </c>
       <c r="G14" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H14" t="n">
-        <v>44.06666666666666</v>
+        <v>55.66666666666667</v>
       </c>
       <c r="I14" t="n">
-        <v>54.46666666666666</v>
+        <v>69.86666666666667</v>
       </c>
       <c r="J14" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="K14" t="n">
         <v>12</v>
       </c>
       <c r="L14" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="M14" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="N14" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
     </row>
     <row r="15">
@@ -1135,42 +1135,42 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="D15" t="n">
-        <v>54</v>
+        <v>104</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>O-23</t>
+          <t>O-25</t>
         </is>
       </c>
       <c r="F15" t="n">
         <v>13</v>
       </c>
       <c r="G15" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H15" t="n">
-        <v>54.46666666666666</v>
+        <v>69.86666666666667</v>
       </c>
       <c r="I15" t="n">
-        <v>55.46666666666666</v>
+        <v>84.86666666666667</v>
       </c>
       <c r="J15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="M15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1183,10 +1183,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="D16" t="n">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -1200,25 +1200,25 @@
         <v>0</v>
       </c>
       <c r="H16" t="n">
+        <v>7</v>
+      </c>
+      <c r="I16" t="n">
+        <v>21.66666666666666</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
         <v>18</v>
       </c>
-      <c r="I16" t="n">
-        <v>32.2</v>
-      </c>
-      <c r="J16" t="n">
+      <c r="M16" t="n">
         <v>12</v>
       </c>
-      <c r="K16" t="n">
-        <v>15</v>
-      </c>
-      <c r="L16" t="n">
-        <v>15</v>
-      </c>
-      <c r="M16" t="n">
+      <c r="N16" t="n">
         <v>14</v>
-      </c>
-      <c r="N16" t="n">
-        <v>15</v>
       </c>
     </row>
     <row r="17">
@@ -1231,10 +1231,10 @@
         <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="D17" t="n">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -1248,22 +1248,22 @@
         <v>1</v>
       </c>
       <c r="H17" t="n">
-        <v>32.2</v>
+        <v>21.66666666666666</v>
       </c>
       <c r="I17" t="n">
-        <v>50.53333333333333</v>
+        <v>25.66666666666666</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K17" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="M17" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -1279,10 +1279,10 @@
         <v>3</v>
       </c>
       <c r="C18" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="D18" t="n">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1296,25 +1296,25 @@
         <v>2</v>
       </c>
       <c r="H18" t="n">
-        <v>50.53333333333333</v>
+        <v>25.66666666666666</v>
       </c>
       <c r="I18" t="n">
-        <v>63.53333333333333</v>
+        <v>27.66666666666666</v>
       </c>
       <c r="J18" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="K18" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N18" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1327,10 +1327,10 @@
         <v>3</v>
       </c>
       <c r="C19" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="D19" t="n">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1344,25 +1344,25 @@
         <v>3</v>
       </c>
       <c r="H19" t="n">
-        <v>63.53333333333333</v>
+        <v>27.66666666666666</v>
       </c>
       <c r="I19" t="n">
-        <v>74.03333333333333</v>
+        <v>47.66666666666666</v>
       </c>
       <c r="J19" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="M19" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="N19" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
     </row>
     <row r="20">
@@ -1375,10 +1375,10 @@
         <v>3</v>
       </c>
       <c r="C20" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="D20" t="n">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -1392,25 +1392,25 @@
         <v>4</v>
       </c>
       <c r="H20" t="n">
-        <v>74.03333333333333</v>
+        <v>47.66666666666666</v>
       </c>
       <c r="I20" t="n">
-        <v>84.03333333333333</v>
+        <v>62</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1423,10 +1423,10 @@
         <v>3</v>
       </c>
       <c r="C21" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="D21" t="n">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1440,25 +1440,25 @@
         <v>5</v>
       </c>
       <c r="H21" t="n">
-        <v>84.03333333333333</v>
+        <v>62</v>
       </c>
       <c r="I21" t="n">
-        <v>95.36666666666666</v>
+        <v>70.5</v>
       </c>
       <c r="J21" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="K21" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="N21" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -1471,10 +1471,10 @@
         <v>4</v>
       </c>
       <c r="C22" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="D22" t="n">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -1488,25 +1488,25 @@
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="I22" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J22" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="K22" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="L22" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
     </row>
     <row r="23">
@@ -1519,10 +1519,10 @@
         <v>4</v>
       </c>
       <c r="C23" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="D23" t="n">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -1536,25 +1536,25 @@
         <v>1</v>
       </c>
       <c r="H23" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I23" t="n">
-        <v>36.75</v>
+        <v>24</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="N23" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -1567,10 +1567,10 @@
         <v>4</v>
       </c>
       <c r="C24" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="D24" t="n">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1584,25 +1584,25 @@
         <v>2</v>
       </c>
       <c r="H24" t="n">
-        <v>36.75</v>
+        <v>24</v>
       </c>
       <c r="I24" t="n">
-        <v>43.41666666666666</v>
+        <v>37.5</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="N24" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -1615,10 +1615,10 @@
         <v>4</v>
       </c>
       <c r="C25" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="D25" t="n">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -1632,25 +1632,25 @@
         <v>3</v>
       </c>
       <c r="H25" t="n">
-        <v>43.41666666666666</v>
+        <v>37.5</v>
       </c>
       <c r="I25" t="n">
-        <v>45.41666666666666</v>
+        <v>45.5</v>
       </c>
       <c r="J25" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -1663,10 +1663,10 @@
         <v>4</v>
       </c>
       <c r="C26" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="D26" t="n">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -1680,73 +1680,73 @@
         <v>4</v>
       </c>
       <c r="H26" t="n">
-        <v>45.41666666666666</v>
+        <v>45.5</v>
       </c>
       <c r="I26" t="n">
-        <v>64.81666666666666</v>
+        <v>50.16666666666666</v>
       </c>
       <c r="J26" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="M26" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="N26" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>J-5</t>
+          <t>J-4</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C27" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="D27" t="n">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>O-50</t>
+          <t>O-45</t>
         </is>
       </c>
       <c r="F27" t="n">
         <v>25</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H27" t="n">
-        <v>22</v>
+        <v>50.16666666666666</v>
       </c>
       <c r="I27" t="n">
-        <v>31</v>
+        <v>62.76666666666667</v>
       </c>
       <c r="J27" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="K27" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="L27" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="M27" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="N27" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="28">
@@ -1759,42 +1759,42 @@
         <v>5</v>
       </c>
       <c r="C28" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="D28" t="n">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>O-51</t>
+          <t>O-50</t>
         </is>
       </c>
       <c r="F28" t="n">
         <v>26</v>
       </c>
       <c r="G28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
+        <v>10</v>
+      </c>
+      <c r="I28" t="n">
         <v>31</v>
       </c>
-      <c r="I28" t="n">
-        <v>50.33333333333333</v>
-      </c>
       <c r="J28" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="K28" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="L28" t="n">
         <v>21</v>
       </c>
       <c r="M28" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
     </row>
     <row r="29">
@@ -1807,39 +1807,39 @@
         <v>5</v>
       </c>
       <c r="C29" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="D29" t="n">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>O-52</t>
+          <t>O-51</t>
         </is>
       </c>
       <c r="F29" t="n">
         <v>27</v>
       </c>
       <c r="G29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H29" t="n">
-        <v>50.33333333333333</v>
+        <v>31</v>
       </c>
       <c r="I29" t="n">
-        <v>61.83333333333333</v>
+        <v>38</v>
       </c>
       <c r="J29" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
         <v>0</v>
@@ -1855,42 +1855,42 @@
         <v>5</v>
       </c>
       <c r="C30" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="D30" t="n">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>O-53</t>
+          <t>O-52</t>
         </is>
       </c>
       <c r="F30" t="n">
         <v>28</v>
       </c>
       <c r="G30" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H30" t="n">
-        <v>61.83333333333333</v>
+        <v>38</v>
       </c>
       <c r="I30" t="n">
-        <v>80.33333333333333</v>
+        <v>55</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
     <row r="31">
@@ -1903,39 +1903,39 @@
         <v>5</v>
       </c>
       <c r="C31" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="D31" t="n">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>O-54</t>
+          <t>O-53</t>
         </is>
       </c>
       <c r="F31" t="n">
         <v>29</v>
       </c>
       <c r="G31" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H31" t="n">
-        <v>80.33333333333333</v>
+        <v>55</v>
       </c>
       <c r="I31" t="n">
-        <v>87.33333333333333</v>
+        <v>65.66666666666667</v>
       </c>
       <c r="J31" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N31" t="n">
         <v>0</v>
@@ -1951,10 +1951,10 @@
         <v>6</v>
       </c>
       <c r="C32" t="n">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="D32" t="n">
-        <v>48</v>
+        <v>69</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -1968,22 +1968,22 @@
         <v>0</v>
       </c>
       <c r="H32" t="n">
+        <v>13</v>
+      </c>
+      <c r="I32" t="n">
         <v>26</v>
       </c>
-      <c r="I32" t="n">
-        <v>39</v>
-      </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="K32" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
         <v>0</v>
@@ -1999,10 +1999,10 @@
         <v>6</v>
       </c>
       <c r="C33" t="n">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="D33" t="n">
-        <v>48</v>
+        <v>69</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -2016,25 +2016,25 @@
         <v>1</v>
       </c>
       <c r="H33" t="n">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="I33" t="n">
-        <v>59</v>
+        <v>30.66666666666667</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="34">
@@ -2047,10 +2047,10 @@
         <v>6</v>
       </c>
       <c r="C34" t="n">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="D34" t="n">
-        <v>48</v>
+        <v>69</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -2064,22 +2064,22 @@
         <v>2</v>
       </c>
       <c r="H34" t="n">
-        <v>59</v>
+        <v>30.66666666666667</v>
       </c>
       <c r="I34" t="n">
-        <v>65</v>
+        <v>48.66666666666667</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="N34" t="n">
         <v>0</v>
@@ -2095,10 +2095,10 @@
         <v>6</v>
       </c>
       <c r="C35" t="n">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="D35" t="n">
-        <v>48</v>
+        <v>69</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -2112,67 +2112,67 @@
         <v>3</v>
       </c>
       <c r="H35" t="n">
-        <v>65</v>
+        <v>48.66666666666667</v>
       </c>
       <c r="I35" t="n">
-        <v>66</v>
+        <v>55.66666666666667</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L35" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="M35" t="n">
         <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>J-7</t>
+          <t>J-6</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C36" t="n">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="D36" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>O-70</t>
+          <t>O-64</t>
         </is>
       </c>
       <c r="F36" t="n">
         <v>34</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H36" t="n">
-        <v>32</v>
+        <v>55.66666666666667</v>
       </c>
       <c r="I36" t="n">
-        <v>36</v>
+        <v>69.66666666666667</v>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
         <v>0</v>
@@ -2191,42 +2191,42 @@
         <v>7</v>
       </c>
       <c r="C37" t="n">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="D37" t="n">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>O-71</t>
+          <t>O-70</t>
         </is>
       </c>
       <c r="F37" t="n">
         <v>35</v>
       </c>
       <c r="G37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="I37" t="n">
-        <v>58.6</v>
+        <v>31</v>
       </c>
       <c r="J37" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="M37" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -2239,42 +2239,42 @@
         <v>7</v>
       </c>
       <c r="C38" t="n">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="D38" t="n">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>O-72</t>
+          <t>O-71</t>
         </is>
       </c>
       <c r="F38" t="n">
         <v>36</v>
       </c>
       <c r="G38" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H38" t="n">
-        <v>58.6</v>
+        <v>31</v>
       </c>
       <c r="I38" t="n">
-        <v>71.93333333333334</v>
+        <v>35</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K38" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L38" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="M38" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
     </row>
     <row r="39">
@@ -2287,42 +2287,42 @@
         <v>7</v>
       </c>
       <c r="C39" t="n">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="D39" t="n">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>O-73</t>
+          <t>O-72</t>
         </is>
       </c>
       <c r="F39" t="n">
         <v>37</v>
       </c>
       <c r="G39" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H39" t="n">
-        <v>71.93333333333334</v>
+        <v>35</v>
       </c>
       <c r="I39" t="n">
-        <v>74.93333333333334</v>
+        <v>45.66666666666666</v>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K39" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="L39" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
     </row>
     <row r="40">
@@ -2335,42 +2335,42 @@
         <v>7</v>
       </c>
       <c r="C40" t="n">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="D40" t="n">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>O-74</t>
+          <t>O-73</t>
         </is>
       </c>
       <c r="F40" t="n">
         <v>38</v>
       </c>
       <c r="G40" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H40" t="n">
-        <v>74.93333333333334</v>
+        <v>45.66666666666666</v>
       </c>
       <c r="I40" t="n">
-        <v>87.93333333333334</v>
+        <v>54.41666666666666</v>
       </c>
       <c r="J40" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="K40" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M40" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="41">
@@ -2383,10 +2383,10 @@
         <v>8</v>
       </c>
       <c r="C41" t="n">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="D41" t="n">
-        <v>112</v>
+        <v>69</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -2400,19 +2400,19 @@
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="I41" t="n">
-        <v>52.66666666666667</v>
+        <v>21</v>
       </c>
       <c r="J41" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="M41" t="n">
         <v>0</v>
@@ -2431,10 +2431,10 @@
         <v>8</v>
       </c>
       <c r="C42" t="n">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="D42" t="n">
-        <v>112</v>
+        <v>69</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -2448,22 +2448,22 @@
         <v>1</v>
       </c>
       <c r="H42" t="n">
-        <v>52.66666666666667</v>
+        <v>21</v>
       </c>
       <c r="I42" t="n">
-        <v>70.41666666666667</v>
+        <v>28</v>
       </c>
       <c r="J42" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="N42" t="n">
         <v>0</v>
@@ -2479,10 +2479,10 @@
         <v>8</v>
       </c>
       <c r="C43" t="n">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="D43" t="n">
-        <v>112</v>
+        <v>69</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -2496,25 +2496,25 @@
         <v>2</v>
       </c>
       <c r="H43" t="n">
-        <v>70.41666666666667</v>
+        <v>28</v>
       </c>
       <c r="I43" t="n">
-        <v>85.41666666666667</v>
+        <v>36.6</v>
       </c>
       <c r="J43" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K43" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="44">
@@ -2527,10 +2527,10 @@
         <v>8</v>
       </c>
       <c r="C44" t="n">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="D44" t="n">
-        <v>112</v>
+        <v>69</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -2544,25 +2544,25 @@
         <v>3</v>
       </c>
       <c r="H44" t="n">
-        <v>85.41666666666667</v>
+        <v>36.6</v>
       </c>
       <c r="I44" t="n">
-        <v>99.91666666666667</v>
+        <v>50.2</v>
       </c>
       <c r="J44" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="K44" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="N44" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="45">
@@ -2575,10 +2575,10 @@
         <v>8</v>
       </c>
       <c r="C45" t="n">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="D45" t="n">
-        <v>112</v>
+        <v>69</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -2592,25 +2592,25 @@
         <v>4</v>
       </c>
       <c r="H45" t="n">
-        <v>99.91666666666667</v>
+        <v>50.2</v>
       </c>
       <c r="I45" t="n">
-        <v>101.9166666666667</v>
+        <v>68.2</v>
       </c>
       <c r="J45" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K45" t="n">
         <v>0</v>
       </c>
       <c r="L45" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="M45" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="N45" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
     </row>
     <row r="46">
@@ -2623,10 +2623,10 @@
         <v>8</v>
       </c>
       <c r="C46" t="n">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="D46" t="n">
-        <v>112</v>
+        <v>69</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -2640,25 +2640,25 @@
         <v>5</v>
       </c>
       <c r="H46" t="n">
-        <v>101.9166666666667</v>
+        <v>68.2</v>
       </c>
       <c r="I46" t="n">
-        <v>124.1166666666667</v>
+        <v>70.2</v>
       </c>
       <c r="J46" t="n">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="K46" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="L46" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="M46" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="N46" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
     </row>
     <row r="47">
@@ -2671,10 +2671,10 @@
         <v>9</v>
       </c>
       <c r="C47" t="n">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="D47" t="n">
-        <v>69</v>
+        <v>111</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -2688,25 +2688,25 @@
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="I47" t="n">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="J47" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="K47" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L47" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -2719,10 +2719,10 @@
         <v>9</v>
       </c>
       <c r="C48" t="n">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="D48" t="n">
-        <v>69</v>
+        <v>111</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -2736,25 +2736,25 @@
         <v>1</v>
       </c>
       <c r="H48" t="n">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="I48" t="n">
-        <v>66</v>
+        <v>43.66666666666666</v>
       </c>
       <c r="J48" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K48" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L48" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
     </row>
     <row r="49">
@@ -2767,10 +2767,10 @@
         <v>9</v>
       </c>
       <c r="C49" t="n">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="D49" t="n">
-        <v>69</v>
+        <v>111</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -2784,25 +2784,25 @@
         <v>2</v>
       </c>
       <c r="H49" t="n">
-        <v>66</v>
+        <v>43.66666666666666</v>
       </c>
       <c r="I49" t="n">
-        <v>80.40000000000001</v>
+        <v>49.66666666666666</v>
       </c>
       <c r="J49" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="L49" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="N49" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -2815,10 +2815,10 @@
         <v>9</v>
       </c>
       <c r="C50" t="n">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="D50" t="n">
-        <v>69</v>
+        <v>111</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -2832,25 +2832,25 @@
         <v>3</v>
       </c>
       <c r="H50" t="n">
-        <v>80.40000000000001</v>
+        <v>49.66666666666666</v>
       </c>
       <c r="I50" t="n">
-        <v>82.40000000000001</v>
+        <v>68.46666666666667</v>
       </c>
       <c r="J50" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="K50" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="M50" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
     </row>
     <row r="51">
@@ -2863,10 +2863,10 @@
         <v>9</v>
       </c>
       <c r="C51" t="n">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="D51" t="n">
-        <v>69</v>
+        <v>111</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
@@ -2880,25 +2880,73 @@
         <v>4</v>
       </c>
       <c r="H51" t="n">
-        <v>82.40000000000001</v>
+        <v>68.46666666666667</v>
       </c>
       <c r="I51" t="n">
-        <v>93</v>
+        <v>86.8</v>
       </c>
       <c r="J51" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="K51" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="L51" t="n">
+        <v>0</v>
+      </c>
+      <c r="M51" t="n">
+        <v>19</v>
+      </c>
+      <c r="N51" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>J-9</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
         <v>9</v>
       </c>
-      <c r="M51" t="n">
-        <v>11</v>
-      </c>
-      <c r="N51" t="n">
-        <v>11</v>
+      <c r="C52" t="n">
+        <v>18</v>
+      </c>
+      <c r="D52" t="n">
+        <v>111</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>O-95</t>
+        </is>
+      </c>
+      <c r="F52" t="n">
+        <v>50</v>
+      </c>
+      <c r="G52" t="n">
+        <v>5</v>
+      </c>
+      <c r="H52" t="n">
+        <v>86.8</v>
+      </c>
+      <c r="I52" t="n">
+        <v>103.4666666666667</v>
+      </c>
+      <c r="J52" t="n">
+        <v>0</v>
+      </c>
+      <c r="K52" t="n">
+        <v>16</v>
+      </c>
+      <c r="L52" t="n">
+        <v>14</v>
+      </c>
+      <c r="M52" t="n">
+        <v>20</v>
+      </c>
+      <c r="N52" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/input/validation/10-5/instance-5.xlsx
+++ b/input/validation/10-5/instance-5.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N52"/>
+  <dimension ref="A1:N50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -514,7 +514,7 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>74</v>
+        <v>52</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -531,22 +531,22 @@
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>13.25</v>
+        <v>5.6</v>
       </c>
       <c r="J2" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="K2" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M2" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="N2" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3">
@@ -562,7 +562,7 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>74</v>
+        <v>52</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -576,25 +576,25 @@
         <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>13.25</v>
+        <v>5.6</v>
       </c>
       <c r="I3" t="n">
-        <v>34.65</v>
+        <v>22.6</v>
       </c>
       <c r="J3" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="L3" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="M3" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4">
@@ -610,7 +610,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>74</v>
+        <v>52</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -624,25 +624,25 @@
         <v>2</v>
       </c>
       <c r="H4" t="n">
-        <v>34.65</v>
+        <v>22.6</v>
       </c>
       <c r="I4" t="n">
-        <v>48.31666666666666</v>
+        <v>40.2</v>
       </c>
       <c r="J4" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="L4" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="M4" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5">
@@ -658,7 +658,7 @@
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>74</v>
+        <v>52</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -672,25 +672,25 @@
         <v>3</v>
       </c>
       <c r="H5" t="n">
-        <v>48.31666666666666</v>
+        <v>40.2</v>
       </c>
       <c r="I5" t="n">
-        <v>56.11666666666666</v>
+        <v>41.2</v>
       </c>
       <c r="J5" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="K5" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="L5" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="M5" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -706,7 +706,7 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>46</v>
+        <v>85</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -723,7 +723,7 @@
         <v>1</v>
       </c>
       <c r="I6" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -732,7 +732,7 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -754,7 +754,7 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>46</v>
+        <v>85</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -768,25 +768,25 @@
         <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I7" t="n">
-        <v>20.4</v>
+        <v>27</v>
       </c>
       <c r="J7" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="K7" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -802,7 +802,7 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>46</v>
+        <v>85</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -816,25 +816,25 @@
         <v>2</v>
       </c>
       <c r="H8" t="n">
-        <v>20.4</v>
+        <v>27</v>
       </c>
       <c r="I8" t="n">
-        <v>27.15</v>
+        <v>36.75</v>
       </c>
       <c r="J8" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L8" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="M8" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9">
@@ -850,7 +850,7 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>46</v>
+        <v>85</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -864,73 +864,73 @@
         <v>3</v>
       </c>
       <c r="H9" t="n">
-        <v>27.15</v>
+        <v>36.75</v>
       </c>
       <c r="I9" t="n">
-        <v>37.4</v>
+        <v>51.08333333333334</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="K9" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="L9" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J-2</t>
+          <t>J-1</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>104</v>
+        <v>85</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>O-20</t>
+          <t>O-14</t>
         </is>
       </c>
       <c r="F10" t="n">
         <v>8</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H10" t="n">
-        <v>5</v>
+        <v>51.08333333333334</v>
       </c>
       <c r="I10" t="n">
-        <v>23.66666666666667</v>
+        <v>70.08333333333334</v>
       </c>
       <c r="J10" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="M10" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N10" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -943,42 +943,42 @@
         <v>2</v>
       </c>
       <c r="C11" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D11" t="n">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>O-21</t>
+          <t>O-20</t>
         </is>
       </c>
       <c r="F11" t="n">
         <v>9</v>
       </c>
       <c r="G11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>23.66666666666667</v>
+        <v>9</v>
       </c>
       <c r="I11" t="n">
-        <v>39.66666666666667</v>
+        <v>25</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K11" t="n">
         <v>16</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
     </row>
     <row r="12">
@@ -991,42 +991,42 @@
         <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D12" t="n">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>O-22</t>
+          <t>O-21</t>
         </is>
       </c>
       <c r="F12" t="n">
         <v>10</v>
       </c>
       <c r="G12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>39.66666666666667</v>
+        <v>25</v>
       </c>
       <c r="I12" t="n">
-        <v>54.66666666666667</v>
+        <v>26</v>
       </c>
       <c r="J12" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L12" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="N12" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1039,42 +1039,42 @@
         <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D13" t="n">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>O-23</t>
+          <t>O-22</t>
         </is>
       </c>
       <c r="F13" t="n">
         <v>11</v>
       </c>
       <c r="G13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H13" t="n">
-        <v>54.66666666666667</v>
+        <v>26</v>
       </c>
       <c r="I13" t="n">
-        <v>55.66666666666667</v>
+        <v>35</v>
       </c>
       <c r="J13" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="K13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14">
@@ -1087,42 +1087,42 @@
         <v>2</v>
       </c>
       <c r="C14" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D14" t="n">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>O-24</t>
+          <t>O-23</t>
         </is>
       </c>
       <c r="F14" t="n">
         <v>12</v>
       </c>
       <c r="G14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H14" t="n">
-        <v>55.66666666666667</v>
+        <v>35</v>
       </c>
       <c r="I14" t="n">
-        <v>69.86666666666667</v>
+        <v>54.8</v>
       </c>
       <c r="J14" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="K14" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="L14" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="M14" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="N14" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="15">
@@ -1135,27 +1135,27 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D15" t="n">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>O-25</t>
+          <t>O-24</t>
         </is>
       </c>
       <c r="F15" t="n">
         <v>13</v>
       </c>
       <c r="G15" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H15" t="n">
-        <v>69.86666666666667</v>
+        <v>54.8</v>
       </c>
       <c r="I15" t="n">
-        <v>84.86666666666667</v>
+        <v>67.8</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1164,61 +1164,61 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J-3</t>
+          <t>J-2</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C16" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D16" t="n">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>O-30</t>
+          <t>O-25</t>
         </is>
       </c>
       <c r="F16" t="n">
         <v>14</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H16" t="n">
-        <v>7</v>
+        <v>67.8</v>
       </c>
       <c r="I16" t="n">
-        <v>21.66666666666666</v>
+        <v>81.8</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1231,42 +1231,42 @@
         <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="D17" t="n">
-        <v>85</v>
+        <v>36</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>O-31</t>
+          <t>O-30</t>
         </is>
       </c>
       <c r="F17" t="n">
         <v>15</v>
       </c>
       <c r="G17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>21.66666666666666</v>
+        <v>25</v>
       </c>
       <c r="I17" t="n">
-        <v>25.66666666666666</v>
+        <v>29</v>
       </c>
       <c r="J17" t="n">
         <v>4</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L17" t="n">
         <v>4</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="18">
@@ -1279,42 +1279,42 @@
         <v>3</v>
       </c>
       <c r="C18" t="n">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="D18" t="n">
-        <v>85</v>
+        <v>36</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>O-32</t>
+          <t>O-31</t>
         </is>
       </c>
       <c r="F18" t="n">
         <v>16</v>
       </c>
       <c r="G18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H18" t="n">
-        <v>25.66666666666666</v>
+        <v>29</v>
       </c>
       <c r="I18" t="n">
-        <v>27.66666666666666</v>
+        <v>35.25</v>
       </c>
       <c r="J18" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="K18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M18" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19">
@@ -1327,42 +1327,42 @@
         <v>3</v>
       </c>
       <c r="C19" t="n">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="D19" t="n">
-        <v>85</v>
+        <v>36</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>O-33</t>
+          <t>O-32</t>
         </is>
       </c>
       <c r="F19" t="n">
         <v>17</v>
       </c>
       <c r="G19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H19" t="n">
-        <v>27.66666666666666</v>
+        <v>35.25</v>
       </c>
       <c r="I19" t="n">
-        <v>47.66666666666666</v>
+        <v>39.25</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K19" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1375,42 +1375,42 @@
         <v>3</v>
       </c>
       <c r="C20" t="n">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="D20" t="n">
-        <v>85</v>
+        <v>36</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>O-34</t>
+          <t>O-33</t>
         </is>
       </c>
       <c r="F20" t="n">
         <v>18</v>
       </c>
       <c r="G20" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H20" t="n">
-        <v>47.66666666666666</v>
+        <v>39.25</v>
       </c>
       <c r="I20" t="n">
-        <v>62</v>
+        <v>44.91666666666666</v>
       </c>
       <c r="J20" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="K20" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21">
@@ -1423,42 +1423,42 @@
         <v>3</v>
       </c>
       <c r="C21" t="n">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="D21" t="n">
-        <v>85</v>
+        <v>36</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>O-35</t>
+          <t>O-34</t>
         </is>
       </c>
       <c r="F21" t="n">
         <v>19</v>
       </c>
       <c r="G21" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H21" t="n">
-        <v>62</v>
+        <v>44.91666666666666</v>
       </c>
       <c r="I21" t="n">
-        <v>70.5</v>
+        <v>53.91666666666666</v>
       </c>
       <c r="J21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="22">
@@ -1471,10 +1471,10 @@
         <v>4</v>
       </c>
       <c r="C22" t="n">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="D22" t="n">
-        <v>69</v>
+        <v>90</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -1488,25 +1488,25 @@
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="I22" t="n">
-        <v>22</v>
+        <v>46.33333333333333</v>
       </c>
       <c r="J22" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="K22" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="L22" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="23">
@@ -1519,10 +1519,10 @@
         <v>4</v>
       </c>
       <c r="C23" t="n">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="D23" t="n">
-        <v>69</v>
+        <v>90</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -1536,22 +1536,22 @@
         <v>1</v>
       </c>
       <c r="H23" t="n">
-        <v>22</v>
+        <v>46.33333333333333</v>
       </c>
       <c r="I23" t="n">
-        <v>24</v>
+        <v>55.33333333333333</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
         <v>0</v>
@@ -1567,10 +1567,10 @@
         <v>4</v>
       </c>
       <c r="C24" t="n">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="D24" t="n">
-        <v>69</v>
+        <v>90</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1584,25 +1584,25 @@
         <v>2</v>
       </c>
       <c r="H24" t="n">
-        <v>24</v>
+        <v>55.33333333333333</v>
       </c>
       <c r="I24" t="n">
-        <v>37.5</v>
+        <v>71.53333333333333</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="K24" t="n">
+        <v>18</v>
+      </c>
+      <c r="L24" t="n">
+        <v>18</v>
+      </c>
+      <c r="M24" t="n">
+        <v>16</v>
+      </c>
+      <c r="N24" t="n">
         <v>15</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" t="n">
-        <v>12</v>
-      </c>
-      <c r="N24" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -1615,10 +1615,10 @@
         <v>4</v>
       </c>
       <c r="C25" t="n">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="D25" t="n">
-        <v>69</v>
+        <v>90</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -1632,25 +1632,25 @@
         <v>3</v>
       </c>
       <c r="H25" t="n">
-        <v>37.5</v>
+        <v>71.53333333333333</v>
       </c>
       <c r="I25" t="n">
-        <v>45.5</v>
+        <v>74.53333333333333</v>
       </c>
       <c r="J25" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="K25" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="26">
@@ -1663,10 +1663,10 @@
         <v>4</v>
       </c>
       <c r="C26" t="n">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="D26" t="n">
-        <v>69</v>
+        <v>90</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -1680,73 +1680,73 @@
         <v>4</v>
       </c>
       <c r="H26" t="n">
-        <v>45.5</v>
+        <v>74.53333333333333</v>
       </c>
       <c r="I26" t="n">
-        <v>50.16666666666666</v>
+        <v>93.78333333333333</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="M26" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="N26" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>J-4</t>
+          <t>J-5</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C27" t="n">
-        <v>9</v>
+        <v>53</v>
       </c>
       <c r="D27" t="n">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>O-45</t>
+          <t>O-50</t>
         </is>
       </c>
       <c r="F27" t="n">
         <v>25</v>
       </c>
       <c r="G27" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>50.16666666666666</v>
+        <v>53</v>
       </c>
       <c r="I27" t="n">
-        <v>62.76666666666667</v>
+        <v>57</v>
       </c>
       <c r="J27" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="K27" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="L27" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="M27" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="N27" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
     </row>
     <row r="28">
@@ -1759,42 +1759,42 @@
         <v>5</v>
       </c>
       <c r="C28" t="n">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="D28" t="n">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>O-50</t>
+          <t>O-51</t>
         </is>
       </c>
       <c r="F28" t="n">
         <v>26</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H28" t="n">
-        <v>10</v>
+        <v>57</v>
       </c>
       <c r="I28" t="n">
-        <v>31</v>
+        <v>69.5</v>
       </c>
       <c r="J28" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="L28" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="N28" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
     </row>
     <row r="29">
@@ -1807,42 +1807,42 @@
         <v>5</v>
       </c>
       <c r="C29" t="n">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="D29" t="n">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>O-51</t>
+          <t>O-52</t>
         </is>
       </c>
       <c r="F29" t="n">
         <v>27</v>
       </c>
       <c r="G29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H29" t="n">
-        <v>31</v>
+        <v>69.5</v>
       </c>
       <c r="I29" t="n">
-        <v>38</v>
+        <v>88</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
     </row>
     <row r="30">
@@ -1855,90 +1855,90 @@
         <v>5</v>
       </c>
       <c r="C30" t="n">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="D30" t="n">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>O-52</t>
+          <t>O-53</t>
         </is>
       </c>
       <c r="F30" t="n">
         <v>28</v>
       </c>
       <c r="G30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H30" t="n">
-        <v>38</v>
+        <v>88</v>
       </c>
       <c r="I30" t="n">
-        <v>55</v>
+        <v>101</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="N30" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>J-5</t>
+          <t>J-6</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C31" t="n">
-        <v>10</v>
+        <v>54</v>
       </c>
       <c r="D31" t="n">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>O-53</t>
+          <t>O-60</t>
         </is>
       </c>
       <c r="F31" t="n">
         <v>29</v>
       </c>
       <c r="G31" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I31" t="n">
-        <v>65.66666666666667</v>
+        <v>62.6</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="K31" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="L31" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="M31" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="32">
@@ -1951,42 +1951,42 @@
         <v>6</v>
       </c>
       <c r="C32" t="n">
-        <v>13</v>
+        <v>54</v>
       </c>
       <c r="D32" t="n">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>O-60</t>
+          <t>O-61</t>
         </is>
       </c>
       <c r="F32" t="n">
         <v>30</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H32" t="n">
-        <v>13</v>
+        <v>62.6</v>
       </c>
       <c r="I32" t="n">
-        <v>26</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="J32" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="K32" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="33">
@@ -1999,42 +1999,42 @@
         <v>6</v>
       </c>
       <c r="C33" t="n">
-        <v>13</v>
+        <v>54</v>
       </c>
       <c r="D33" t="n">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>O-61</t>
+          <t>O-62</t>
         </is>
       </c>
       <c r="F33" t="n">
         <v>31</v>
       </c>
       <c r="G33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H33" t="n">
-        <v>26</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="I33" t="n">
-        <v>30.66666666666667</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M33" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
     </row>
     <row r="34">
@@ -2047,42 +2047,42 @@
         <v>6</v>
       </c>
       <c r="C34" t="n">
-        <v>13</v>
+        <v>54</v>
       </c>
       <c r="D34" t="n">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>O-62</t>
+          <t>O-63</t>
         </is>
       </c>
       <c r="F34" t="n">
         <v>32</v>
       </c>
       <c r="G34" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H34" t="n">
-        <v>30.66666666666667</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="I34" t="n">
-        <v>48.66666666666667</v>
+        <v>97.34999999999999</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="L34" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="M34" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
     </row>
     <row r="35">
@@ -2095,90 +2095,90 @@
         <v>6</v>
       </c>
       <c r="C35" t="n">
-        <v>13</v>
+        <v>54</v>
       </c>
       <c r="D35" t="n">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>O-63</t>
+          <t>O-64</t>
         </is>
       </c>
       <c r="F35" t="n">
         <v>33</v>
       </c>
       <c r="G35" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H35" t="n">
-        <v>48.66666666666667</v>
+        <v>97.34999999999999</v>
       </c>
       <c r="I35" t="n">
-        <v>55.66666666666667</v>
+        <v>98.34999999999999</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K35" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="L35" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>J-6</t>
+          <t>J-7</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C36" t="n">
-        <v>13</v>
+        <v>59</v>
       </c>
       <c r="D36" t="n">
-        <v>69</v>
+        <v>100</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>O-64</t>
+          <t>O-70</t>
         </is>
       </c>
       <c r="F36" t="n">
         <v>34</v>
       </c>
       <c r="G36" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>55.66666666666667</v>
+        <v>59</v>
       </c>
       <c r="I36" t="n">
-        <v>69.66666666666667</v>
+        <v>77.2</v>
       </c>
       <c r="J36" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="K36" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
     <row r="37">
@@ -2191,42 +2191,42 @@
         <v>7</v>
       </c>
       <c r="C37" t="n">
-        <v>15</v>
+        <v>59</v>
       </c>
       <c r="D37" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>O-70</t>
+          <t>O-71</t>
         </is>
       </c>
       <c r="F37" t="n">
         <v>35</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H37" t="n">
-        <v>15</v>
+        <v>77.2</v>
       </c>
       <c r="I37" t="n">
-        <v>31</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="J37" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="K37" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="L37" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="38">
@@ -2239,42 +2239,42 @@
         <v>7</v>
       </c>
       <c r="C38" t="n">
-        <v>15</v>
+        <v>59</v>
       </c>
       <c r="D38" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>O-71</t>
+          <t>O-72</t>
         </is>
       </c>
       <c r="F38" t="n">
         <v>36</v>
       </c>
       <c r="G38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H38" t="n">
-        <v>31</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="I38" t="n">
-        <v>35</v>
+        <v>102.4</v>
       </c>
       <c r="J38" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
         <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
     </row>
     <row r="39">
@@ -2287,39 +2287,39 @@
         <v>7</v>
       </c>
       <c r="C39" t="n">
-        <v>15</v>
+        <v>59</v>
       </c>
       <c r="D39" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>O-72</t>
+          <t>O-73</t>
         </is>
       </c>
       <c r="F39" t="n">
         <v>37</v>
       </c>
       <c r="G39" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H39" t="n">
-        <v>35</v>
+        <v>102.4</v>
       </c>
       <c r="I39" t="n">
-        <v>45.66666666666666</v>
+        <v>113.4</v>
       </c>
       <c r="J39" t="n">
         <v>10</v>
       </c>
       <c r="K39" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N39" t="n">
         <v>13</v>
@@ -2335,87 +2335,87 @@
         <v>7</v>
       </c>
       <c r="C40" t="n">
-        <v>15</v>
+        <v>59</v>
       </c>
       <c r="D40" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>O-73</t>
+          <t>O-74</t>
         </is>
       </c>
       <c r="F40" t="n">
         <v>38</v>
       </c>
       <c r="G40" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H40" t="n">
-        <v>45.66666666666666</v>
+        <v>113.4</v>
       </c>
       <c r="I40" t="n">
-        <v>54.41666666666666</v>
+        <v>126</v>
       </c>
       <c r="J40" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="K40" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="L40" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="N40" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>J-8</t>
+          <t>J-7</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C41" t="n">
-        <v>17</v>
+        <v>59</v>
       </c>
       <c r="D41" t="n">
-        <v>69</v>
+        <v>100</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>O-80</t>
+          <t>O-75</t>
         </is>
       </c>
       <c r="F41" t="n">
         <v>39</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H41" t="n">
-        <v>17</v>
+        <v>126</v>
       </c>
       <c r="I41" t="n">
-        <v>21</v>
+        <v>135.3333333333333</v>
       </c>
       <c r="J41" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K41" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L41" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="N41" t="n">
         <v>0</v>
@@ -2431,39 +2431,39 @@
         <v>8</v>
       </c>
       <c r="C42" t="n">
-        <v>17</v>
+        <v>61</v>
       </c>
       <c r="D42" t="n">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>O-81</t>
+          <t>O-80</t>
         </is>
       </c>
       <c r="F42" t="n">
         <v>40</v>
       </c>
       <c r="G42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>21</v>
+        <v>61</v>
       </c>
       <c r="I42" t="n">
-        <v>28</v>
+        <v>78</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="L42" t="n">
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
         <v>0</v>
@@ -2479,42 +2479,42 @@
         <v>8</v>
       </c>
       <c r="C43" t="n">
-        <v>17</v>
+        <v>61</v>
       </c>
       <c r="D43" t="n">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>O-82</t>
+          <t>O-81</t>
         </is>
       </c>
       <c r="F43" t="n">
         <v>41</v>
       </c>
       <c r="G43" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H43" t="n">
-        <v>28</v>
+        <v>78</v>
       </c>
       <c r="I43" t="n">
-        <v>36.6</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="J43" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="K43" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="L43" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="M43" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="N43" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
     </row>
     <row r="44">
@@ -2527,42 +2527,42 @@
         <v>8</v>
       </c>
       <c r="C44" t="n">
-        <v>17</v>
+        <v>61</v>
       </c>
       <c r="D44" t="n">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>O-83</t>
+          <t>O-82</t>
         </is>
       </c>
       <c r="F44" t="n">
         <v>42</v>
       </c>
       <c r="G44" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H44" t="n">
-        <v>36.6</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="I44" t="n">
-        <v>50.2</v>
+        <v>100.4</v>
       </c>
       <c r="J44" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="L44" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="N44" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -2575,90 +2575,90 @@
         <v>8</v>
       </c>
       <c r="C45" t="n">
-        <v>17</v>
+        <v>61</v>
       </c>
       <c r="D45" t="n">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>O-84</t>
+          <t>O-83</t>
         </is>
       </c>
       <c r="F45" t="n">
         <v>43</v>
       </c>
       <c r="G45" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H45" t="n">
-        <v>50.2</v>
+        <v>100.4</v>
       </c>
       <c r="I45" t="n">
-        <v>68.2</v>
+        <v>112.9</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="L45" t="n">
+        <v>11</v>
+      </c>
+      <c r="M45" t="n">
         <v>15</v>
       </c>
-      <c r="M45" t="n">
-        <v>19</v>
-      </c>
       <c r="N45" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>J-8</t>
+          <t>J-9</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C46" t="n">
-        <v>17</v>
+        <v>66</v>
       </c>
       <c r="D46" t="n">
-        <v>69</v>
+        <v>42</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>O-85</t>
+          <t>O-90</t>
         </is>
       </c>
       <c r="F46" t="n">
         <v>44</v>
       </c>
       <c r="G46" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>68.2</v>
+        <v>66</v>
       </c>
       <c r="I46" t="n">
-        <v>70.2</v>
+        <v>69</v>
       </c>
       <c r="J46" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L46" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M46" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N46" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="47">
@@ -2671,42 +2671,42 @@
         <v>9</v>
       </c>
       <c r="C47" t="n">
-        <v>18</v>
+        <v>66</v>
       </c>
       <c r="D47" t="n">
-        <v>111</v>
+        <v>42</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>O-90</t>
+          <t>O-91</t>
         </is>
       </c>
       <c r="F47" t="n">
         <v>45</v>
       </c>
       <c r="G47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H47" t="n">
-        <v>18</v>
+        <v>69</v>
       </c>
       <c r="I47" t="n">
-        <v>37</v>
+        <v>76</v>
       </c>
       <c r="J47" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="K47" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M47" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="48">
@@ -2719,33 +2719,33 @@
         <v>9</v>
       </c>
       <c r="C48" t="n">
-        <v>18</v>
+        <v>66</v>
       </c>
       <c r="D48" t="n">
-        <v>111</v>
+        <v>42</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>O-91</t>
+          <t>O-92</t>
         </is>
       </c>
       <c r="F48" t="n">
         <v>46</v>
       </c>
       <c r="G48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H48" t="n">
-        <v>37</v>
+        <v>76</v>
       </c>
       <c r="I48" t="n">
-        <v>43.66666666666666</v>
+        <v>86</v>
       </c>
       <c r="J48" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L48" t="n">
         <v>0</v>
@@ -2754,7 +2754,7 @@
         <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="49">
@@ -2767,39 +2767,39 @@
         <v>9</v>
       </c>
       <c r="C49" t="n">
-        <v>18</v>
+        <v>66</v>
       </c>
       <c r="D49" t="n">
-        <v>111</v>
+        <v>42</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>O-92</t>
+          <t>O-93</t>
         </is>
       </c>
       <c r="F49" t="n">
         <v>47</v>
       </c>
       <c r="G49" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H49" t="n">
-        <v>43.66666666666666</v>
+        <v>86</v>
       </c>
       <c r="I49" t="n">
-        <v>49.66666666666666</v>
+        <v>92</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L49" t="n">
         <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="N49" t="n">
         <v>0</v>
@@ -2815,137 +2815,41 @@
         <v>9</v>
       </c>
       <c r="C50" t="n">
-        <v>18</v>
+        <v>66</v>
       </c>
       <c r="D50" t="n">
-        <v>111</v>
+        <v>42</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>O-93</t>
+          <t>O-94</t>
         </is>
       </c>
       <c r="F50" t="n">
         <v>48</v>
       </c>
       <c r="G50" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H50" t="n">
-        <v>49.66666666666666</v>
+        <v>92</v>
       </c>
       <c r="I50" t="n">
-        <v>68.46666666666667</v>
+        <v>100</v>
       </c>
       <c r="J50" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="K50" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="L50" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>J-9</t>
-        </is>
-      </c>
-      <c r="B51" t="n">
-        <v>9</v>
-      </c>
-      <c r="C51" t="n">
-        <v>18</v>
-      </c>
-      <c r="D51" t="n">
-        <v>111</v>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>O-94</t>
-        </is>
-      </c>
-      <c r="F51" t="n">
-        <v>49</v>
-      </c>
-      <c r="G51" t="n">
-        <v>4</v>
-      </c>
-      <c r="H51" t="n">
-        <v>68.46666666666667</v>
-      </c>
-      <c r="I51" t="n">
-        <v>86.8</v>
-      </c>
-      <c r="J51" t="n">
-        <v>17</v>
-      </c>
-      <c r="K51" t="n">
-        <v>19</v>
-      </c>
-      <c r="L51" t="n">
-        <v>0</v>
-      </c>
-      <c r="M51" t="n">
-        <v>19</v>
-      </c>
-      <c r="N51" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>J-9</t>
-        </is>
-      </c>
-      <c r="B52" t="n">
-        <v>9</v>
-      </c>
-      <c r="C52" t="n">
-        <v>18</v>
-      </c>
-      <c r="D52" t="n">
-        <v>111</v>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>O-95</t>
-        </is>
-      </c>
-      <c r="F52" t="n">
-        <v>50</v>
-      </c>
-      <c r="G52" t="n">
-        <v>5</v>
-      </c>
-      <c r="H52" t="n">
-        <v>86.8</v>
-      </c>
-      <c r="I52" t="n">
-        <v>103.4666666666667</v>
-      </c>
-      <c r="J52" t="n">
-        <v>0</v>
-      </c>
-      <c r="K52" t="n">
-        <v>16</v>
-      </c>
-      <c r="L52" t="n">
-        <v>14</v>
-      </c>
-      <c r="M52" t="n">
-        <v>20</v>
-      </c>
-      <c r="N52" t="n">
         <v>0</v>
       </c>
     </row>
